--- a/forms/app/group_counseling.xlsx
+++ b/forms/app/group_counseling.xlsx
@@ -13,17 +13,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="115">
   <si>
     <t>form_title</t>
   </si>
   <si>
+    <t>list_name</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
-    <t>list_name</t>
-  </si>
-  <si>
     <t>form_id</t>
   </si>
   <si>
@@ -36,12 +36,12 @@
     <t>path</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>instance_name</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>label::en</t>
   </si>
   <si>
@@ -51,6 +51,9 @@
     <t>required</t>
   </si>
   <si>
+    <t>Group Counseling</t>
+  </si>
+  <si>
     <t>relevant</t>
   </si>
   <si>
@@ -66,9 +69,6 @@
     <t>constraint_message::en</t>
   </si>
   <si>
-    <t>Group Counseling</t>
-  </si>
-  <si>
     <t>constraint_message::sw</t>
   </si>
   <si>
@@ -90,15 +90,15 @@
     <t>repeat_count</t>
   </si>
   <si>
+    <t>begin group</t>
+  </si>
+  <si>
     <t>group_counseling</t>
   </si>
   <si>
     <t>pages</t>
   </si>
   <si>
-    <t>begin group</t>
-  </si>
-  <si>
     <t>data</t>
   </si>
   <si>
@@ -154,6 +154,49 @@
   </si>
   <si>
     <t>../inputs/user/facility_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">begin group </t>
+  </si>
+  <si>
+    <t>covid19_intro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precautionary measures when visiting a client  </t>
+  </si>
+  <si>
+    <t>Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>covid19_intro_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Corona virus to one another. Therefore, make sure you consider the following while you conduct the visits:  
+•        Wash your hands with soap/sanitizer as many time as you can while at home, once you are at the client’s house and when you leave.
+•        Keep a 2 meters distance while talking to your clients.
+•        Don’t shake hands with your clients. 
+•        Avoid group gatherings.
+•        Provide the service at the open space and if it should be inside, make sure the windows and doors are open. 
+•        Cover your mouth with a towel or elbow when you sneeze or cough. 
+•        Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.&lt;/span&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Kama mhudumu wa afya ya jamii, una jukumu la kuhakikisha unatoa elimu ya afya ya jamii na huduma huku ukijikinga ili kuepusha kusambaa kwa maambukizi ya korona kutoka kwa mtu mmoja kwenda kwa mwengine. Hivyo hakikisha unazingatia yafuatayo wakati ukiwa unatoa huduma:
+•        Osha mikono yako kwa maji na sabuni au kutumia vitakasa mikono mara nyingi kadiri unavyoweza ukiwa nyumbani kwako,nyumbani kwa mteja wako na pindi ukimaliza kutoa huduma. 
+•        Hakikisha kuna umbali wa mita mbili kati yako na mteja wako unayeenda kumtembelea 
+•        Pindi ukiongea na wateja wako , usishikane mikono. 
+•        Epuka mikusanyiko. 
+•        Toa huduma katika maeneo yaliyo wazi na ikitokea ukafanya ndani hakikisha milango na madirisha yanakuwa wazi.  
+•        Funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa. 
+•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end group </t>
   </si>
   <si>
     <t>chv_group_counseling</t>
@@ -349,13 +392,13 @@
       <name val="Cambria"/>
     </font>
     <font>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
+      <sz val="10.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -371,21 +414,27 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF1D1C1D"/>
+      <name val="Slack-Lato"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
-    <font>
-      <sz val="10.0"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -402,48 +451,57 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -451,9 +509,9 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -462,11 +520,8 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -696,13 +751,13 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="6" t="s">
@@ -712,19 +767,19 @@
         <v>11</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>18</v>
@@ -759,7 +814,7 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>29</v>
@@ -768,22 +823,22 @@
         <v>30</v>
       </c>
       <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11" t="b">
+      <c r="E2" s="5"/>
+      <c r="F2" s="10" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
       <c r="S2" s="5"/>
       <c r="T2" s="5"/>
@@ -796,7 +851,7 @@
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>31</v>
@@ -805,19 +860,19 @@
         <v>30</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
@@ -839,19 +894,19 @@
         <v>34</v>
       </c>
       <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
@@ -873,19 +928,19 @@
         <v>36</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
@@ -901,25 +956,25 @@
         <v>32</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
@@ -939,19 +994,19 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
@@ -971,19 +1026,19 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
@@ -1003,23 +1058,23 @@
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="12" t="s">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
@@ -1034,28 +1089,28 @@
       <c r="A10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="12" t="s">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
@@ -1075,23 +1130,23 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="12" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
@@ -1103,613 +1158,696 @@
       <c r="Z11" s="5"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="K13" s="18" t="s">
+      <c r="E15" s="18"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="17"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="17"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" s="17"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K30" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K31" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="17"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="C34" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="K20" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="14"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="K23" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J24" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="K24" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C33:D33"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1727,11 +1865,11 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
+      <c r="A1" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>9</v>
@@ -1823,8 +1961,8 @@
       <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>7</v>
+      <c r="F1" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1849,13 +1987,13 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>28</v>

--- a/forms/app/group_counseling.xlsx
+++ b/forms/app/group_counseling.xlsx
@@ -1,19 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6325"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="120">
   <si>
     <t>type</t>
   </si>
@@ -381,54 +389,67 @@
   <si>
     <t>data</t>
   </si>
+  <si>
+    <t>note_to_chv</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f;font-weight: bold"&gt;Muhudumu wa afya ya Jamii anaushauriwa kutumia Bango Kitita au Muongozo wa Michezo na mawasiliano kuaandaa mkutano wa kikundi kulingana na uhitaji wa eneo lake, Pia anaweza kuomba muongozo/ushauri kutoka kwa msimamizi wake jinsi ya kuandaa ajenda ya ushauri wa kikundi.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f;font-weight: bold"&gt;CHV is advised to use Bangokitita or play and communication guide to prepare for group counseling with regards to the needs of his/her catchment area.He /she can also ask for guidance from his/her supervisor on how to create the agendas for the Group counselling session.&lt;/span&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="10">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
     </font>
@@ -438,7 +459,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -454,119 +475,84 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
+      <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -756,23 +742,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z37"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="26.43"/>
-    <col customWidth="1" min="3" max="3" width="26.86"/>
-    <col customWidth="1" min="4" max="4" width="31.43"/>
-    <col customWidth="1" min="9" max="9" width="26.14"/>
+    <col min="2" max="2" width="26.40625" customWidth="1"/>
+    <col min="3" max="3" width="26.86328125" customWidth="1"/>
+    <col min="4" max="4" width="31.40625" customWidth="1"/>
+    <col min="9" max="9" width="26.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -834,7 +823,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="13">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -871,7 +860,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="13">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -905,7 +894,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="13">
       <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
@@ -939,7 +928,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="13">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
@@ -973,7 +962,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="13">
       <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
@@ -1007,7 +996,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="13">
       <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
@@ -1039,7 +1028,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="13">
       <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
@@ -1071,7 +1060,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="13">
       <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
@@ -1107,7 +1096,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="13">
       <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
@@ -1143,7 +1132,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" ht="13">
       <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
@@ -1179,7 +1168,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="13">
       <c r="A12" s="8" t="s">
         <v>36</v>
       </c>
@@ -1211,7 +1200,7 @@
       <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="13">
       <c r="A13" s="8" t="s">
         <v>37</v>
       </c>
@@ -1243,7 +1232,7 @@
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="13">
       <c r="A14" s="9" t="s">
         <v>38</v>
       </c>
@@ -1272,7 +1261,7 @@
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
+    <row r="15" spans="1:26" ht="22.5" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>42</v>
       </c>
@@ -1301,7 +1290,7 @@
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" ht="13">
       <c r="A16" s="9" t="s">
         <v>46</v>
       </c>
@@ -1326,16 +1315,17 @@
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" ht="13">
       <c r="A17" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="27" t="s">
         <v>19</v>
       </c>
+      <c r="D17" s="27"/>
       <c r="E17" s="15"/>
       <c r="F17" s="16"/>
       <c r="G17" s="14" t="s">
@@ -1352,34 +1342,24 @@
       <c r="P17" s="16"/>
       <c r="Q17" s="16"/>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>53</v>
+    <row r="18" spans="1:17" s="20" customFormat="1" ht="13">
+      <c r="A18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>118</v>
       </c>
       <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
       <c r="H18" s="16"/>
-      <c r="I18" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>56</v>
-      </c>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
@@ -1387,18 +1367,18 @@
       <c r="P18" s="16"/>
       <c r="Q18" s="16"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" ht="13">
       <c r="A19" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>53</v>
@@ -1410,10 +1390,10 @@
         <v>54</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
@@ -1422,18 +1402,18 @@
       <c r="P19" s="16"/>
       <c r="Q19" s="16"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" ht="13">
       <c r="A20" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>53</v>
@@ -1445,10 +1425,10 @@
         <v>54</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
@@ -1457,33 +1437,33 @@
       <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" ht="13">
       <c r="A21" s="14" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="19"/>
+      <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
-      <c r="I21" s="14" t="s">
-        <v>70</v>
+      <c r="I21" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
@@ -1492,31 +1472,33 @@
       <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" ht="13">
       <c r="A22" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="16"/>
+      <c r="F22" s="19"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
+      <c r="I22" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="J22" s="18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
@@ -1525,23 +1507,32 @@
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" ht="13">
       <c r="A23" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>78</v>
+        <v>49</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>73</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="14"/>
+        <v>74</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
       <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
+      <c r="J23" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>77</v>
+      </c>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
       <c r="N23" s="16"/>
@@ -1549,32 +1540,24 @@
       <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" ht="13">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>82</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="27"/>
       <c r="E24" s="14"/>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
-      <c r="I24" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>85</v>
-      </c>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
@@ -1582,18 +1565,18 @@
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" ht="13">
       <c r="A25" s="14" t="s">
         <v>79</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="16"/>
@@ -1615,23 +1598,32 @@
       <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" ht="13">
       <c r="A26" s="14" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>19</v>
+        <v>87</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="E26" s="14"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="18"/>
+      <c r="I26" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>85</v>
+      </c>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
@@ -1639,16 +1631,17 @@
       <c r="P26" s="16"/>
       <c r="Q26" s="16"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" ht="13">
       <c r="A27" s="14" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="27" t="s">
         <v>19</v>
       </c>
+      <c r="D27" s="27"/>
       <c r="E27" s="14"/>
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
@@ -1663,32 +1656,24 @@
       <c r="P27" s="16"/>
       <c r="Q27" s="16"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" ht="13">
       <c r="A28" s="14" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>92</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="27"/>
       <c r="E28" s="14"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
-      <c r="I28" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="K28" s="18" t="s">
-        <v>85</v>
-      </c>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="18"/>
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
@@ -1696,18 +1681,18 @@
       <c r="P28" s="16"/>
       <c r="Q28" s="16"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" ht="13">
       <c r="A29" s="14" t="s">
         <v>79</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="16"/>
@@ -1729,23 +1714,32 @@
       <c r="P29" s="16"/>
       <c r="Q29" s="16"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" ht="13">
       <c r="A30" s="14" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>19</v>
+        <v>94</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
+      <c r="I30" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>85</v>
+      </c>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
@@ -1753,16 +1747,17 @@
       <c r="P30" s="16"/>
       <c r="Q30" s="16"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" ht="13">
       <c r="A31" s="14" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="27" t="s">
         <v>19</v>
       </c>
+      <c r="D31" s="27"/>
       <c r="E31" s="14"/>
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
@@ -1777,32 +1772,24 @@
       <c r="P31" s="16"/>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" ht="13">
       <c r="A32" s="14" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>99</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="27"/>
       <c r="E32" s="14"/>
       <c r="F32" s="16"/>
       <c r="G32" s="16"/>
       <c r="H32" s="16"/>
-      <c r="I32" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="K32" s="18" t="s">
-        <v>85</v>
-      </c>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
@@ -1810,18 +1797,18 @@
       <c r="P32" s="16"/>
       <c r="Q32" s="16"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:17" ht="13">
       <c r="A33" s="14" t="s">
         <v>79</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="16"/>
@@ -1843,18 +1830,18 @@
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:17" ht="13">
       <c r="A34" s="14" t="s">
         <v>79</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="16"/>
@@ -1876,23 +1863,32 @@
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:17" ht="13">
       <c r="A35" s="14" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="15"/>
+        <v>104</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="14"/>
       <c r="F35" s="16"/>
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
+      <c r="I35" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="J35" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>85</v>
+      </c>
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
@@ -1900,18 +1896,18 @@
       <c r="P35" s="16"/>
       <c r="Q35" s="16"/>
     </row>
-    <row r="36">
-      <c r="A36" s="18" t="s">
+    <row r="36" spans="1:17" ht="13">
+      <c r="A36" s="14" t="s">
         <v>27</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="15"/>
       <c r="F36" s="16"/>
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
@@ -1925,32 +1921,58 @@
       <c r="P36" s="16"/>
       <c r="Q36" s="16"/>
     </row>
+    <row r="37" spans="1:17" ht="13">
+      <c r="A37" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C36:D36"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C28:D28"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C35:D35"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z6"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="20.57"/>
-    <col customWidth="1" min="3" max="3" width="26.43"/>
+    <col min="2" max="2" width="20.54296875" customWidth="1"/>
+    <col min="3" max="3" width="26.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="22" t="s">
         <v>106</v>
       </c>
@@ -1986,52 +2008,53 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="A4" s="24"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.86"/>
+    <col min="1" max="1" width="17.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="25" t="s">
         <v>107</v>
       </c>
@@ -2071,13 +2094,14 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
         <v>114</v>
       </c>
+      <c r="C2" s="27"/>
       <c r="D2" s="24" t="s">
         <v>115</v>
       </c>
@@ -2089,6 +2113,6 @@
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>